--- a/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/gemini_gemini-3-pro-preview-thinking_judge_medium__vs__kimi_kimi-k2.6_judge_high.xlsx
+++ b/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/gemini_gemini-3-pro-preview-thinking_judge_medium__vs__kimi_kimi-k2.6_judge_high.xlsx
@@ -2056,33 +2056,35 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>10032.12404204533</v>
+        <v>12523.92487495672</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01041701762005687</v>
+        <v>1889.051124977414</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2121,33 +2123,35 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>2333.522041037213</v>
+        <v>14398.25245802058</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01070799771696329</v>
+        <v>2208.534208999481</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2186,33 +2190,35 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>6766.414042038377</v>
+        <v>13275.98933398258</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01200003316625953</v>
+        <v>1360.558916989248</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2251,33 +2257,35 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>17457.90899998974</v>
+        <v>11901.44854201935</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01458398764953017</v>
+        <v>1493.047708005179</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2316,33 +2324,35 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>38088.34241598379</v>
+        <v>14254.37591603259</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0190000282600522</v>
+        <v>1531.887667020783</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2381,33 +2391,35 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>27723.15575001994</v>
+        <v>12798.30283299088</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01129100564867258</v>
+        <v>1499.043999996502</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2446,33 +2458,35 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>5626.011875050608</v>
+        <v>13743.25470800977</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01474999589845538</v>
+        <v>1645.668040961027</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2511,33 +2525,35 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.004208006430417299</v>
+        <v>13157.06337499432</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01533294562250376</v>
+        <v>1514.033499988727</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2576,33 +2592,35 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>0.002916960511356592</v>
+        <v>14780.20704200026</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01075002364814281</v>
+        <v>1575.343291973695</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2641,33 +2659,35 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>11864.31883298792</v>
+        <v>12616.21704197023</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01116597559303045</v>
+        <v>1224.478832969908</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2706,33 +2726,35 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>9585.873832984362</v>
+        <v>11603.08308299864</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01154199708253145</v>
+        <v>1849.472415982746</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2771,33 +2793,35 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>3432.569040975068</v>
+        <v>10960.33191698371</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03137497697025537</v>
+        <v>1055.892832984682</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2836,33 +2860,35 @@
       <c r="H14" t="b">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>28494.99395897146</v>
+        <v>16539.13354204269</v>
       </c>
       <c r="M14" t="n">
-        <v>0.007583003025501966</v>
+        <v>1757.322875026148</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2901,33 +2927,35 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>277.1219169953838</v>
+        <v>13738.17987495568</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01083401730284095</v>
+        <v>1041.787791007664</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2966,33 +2994,35 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>12436.49758305401</v>
+        <v>13145.17404098297</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01129199517890811</v>
+        <v>1801.036416029092</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3031,33 +3061,35 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>117769.3030829541</v>
+        <v>13366.00612499751</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0118750031106174</v>
+        <v>1310.986792028416</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3096,33 +3128,35 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>9543.781915970612</v>
+        <v>11944.8535409756</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01266697654500604</v>
+        <v>1968.272208003327</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
